--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,45 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441445</v>
+        <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759426</v>
+        <v>759415</v>
       </c>
       <c r="R3" t="n">
-        <v>7189499</v>
+        <v>7189526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441443</v>
+        <v>127441445</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759514</v>
+        <v>759426</v>
       </c>
       <c r="R4" t="n">
-        <v>7189412</v>
+        <v>7189499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,53 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441417</v>
+        <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759415</v>
+        <v>759514</v>
       </c>
       <c r="R5" t="n">
-        <v>7189526</v>
+        <v>7189412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,45 +1186,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R7" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R8" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441435</v>
+        <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759492</v>
+        <v>759332</v>
       </c>
       <c r="R9" t="n">
-        <v>7189426</v>
+        <v>7189575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441442</v>
+        <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759523</v>
+        <v>759492</v>
       </c>
       <c r="R10" t="n">
-        <v>7189420</v>
+        <v>7189426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,53 +1600,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441394</v>
+        <v>127441442</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759332</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7189575</v>
+        <v>7189420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,11 +1671,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1700,7 @@
         <v>127441450</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>80021</v>
+        <v>91688</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R13" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>91684</v>
+        <v>80025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R14" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>91280</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441419</v>
+        <v>127441399</v>
       </c>
       <c r="B20" t="n">
-        <v>91276</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,34 +2523,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759497</v>
+        <v>759246</v>
       </c>
       <c r="R20" t="n">
-        <v>7189429</v>
+        <v>7189362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,53 +2622,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R21" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,11 +2693,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2722,7 +2722,7 @@
         <v>127441436</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,53 +3036,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R25" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,11 +3107,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3133,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441437</v>
+        <v>127441398</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759369</v>
+        <v>759258</v>
       </c>
       <c r="R26" t="n">
-        <v>7189531</v>
+        <v>7189373</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,6 +3212,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3246,7 +3246,7 @@
         <v>127441418</v>
       </c>
       <c r="B27" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441393</v>
+        <v>127441405</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,34 +3558,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759507</v>
+        <v>759321</v>
       </c>
       <c r="R30" t="n">
-        <v>7189390</v>
+        <v>7189301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3618,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3644,53 +3657,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441405</v>
+        <v>127441449</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759321</v>
+        <v>759381</v>
       </c>
       <c r="R31" t="n">
-        <v>7189301</v>
+        <v>7189520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3728,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,27 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441432</v>
+        <v>127441448</v>
       </c>
       <c r="B32" t="n">
-        <v>91733</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759436</v>
+        <v>759412</v>
       </c>
       <c r="R32" t="n">
-        <v>7189501</v>
+        <v>7189523</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,32 +3851,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441448</v>
+        <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>91737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759412</v>
+        <v>759436</v>
       </c>
       <c r="R33" t="n">
-        <v>7189523</v>
+        <v>7189501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,53 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441417</v>
+        <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759415</v>
+        <v>759426</v>
       </c>
       <c r="R3" t="n">
-        <v>7189526</v>
+        <v>7189499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441445</v>
+        <v>127441443</v>
       </c>
       <c r="B4" t="n">
         <v>98447</v>
@@ -930,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759426</v>
+        <v>759514</v>
       </c>
       <c r="R4" t="n">
-        <v>7189499</v>
+        <v>7189412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,45 +979,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441443</v>
+        <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759514</v>
+        <v>759415</v>
       </c>
       <c r="R5" t="n">
-        <v>7189412</v>
+        <v>7189526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,53 +1186,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R7" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,45 +1283,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R8" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1362,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B13" t="n">
-        <v>91688</v>
+        <v>80025</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R13" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B14" t="n">
-        <v>80025</v>
+        <v>91688</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R14" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R17" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R18" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>91280</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R19" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,53 +2512,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R20" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>91280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R21" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,45 +3036,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441437</v>
+        <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759369</v>
+        <v>759258</v>
       </c>
       <c r="R25" t="n">
-        <v>7189531</v>
+        <v>7189373</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,6 +3115,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,10 +3146,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441398</v>
+        <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3157,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,7 +3179,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3176,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759258</v>
+        <v>759318</v>
       </c>
       <c r="R26" t="n">
-        <v>7189373</v>
+        <v>7189338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,7 +3229,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,53 +3256,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441418</v>
+        <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759318</v>
+        <v>759369</v>
       </c>
       <c r="R27" t="n">
-        <v>7189338</v>
+        <v>7189531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,11 +3327,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,53 +3547,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441405</v>
+        <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759321</v>
+        <v>759381</v>
       </c>
       <c r="R30" t="n">
-        <v>7189301</v>
+        <v>7189520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,11 +3618,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,7 +3644,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441449</v>
+        <v>127441448</v>
       </c>
       <c r="B31" t="n">
         <v>98447</v>
@@ -3692,10 +3679,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759381</v>
+        <v>759412</v>
       </c>
       <c r="R31" t="n">
-        <v>7189520</v>
+        <v>7189523</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,32 +3741,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441448</v>
+        <v>127441432</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>91737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759412</v>
+        <v>759436</v>
       </c>
       <c r="R32" t="n">
-        <v>7189523</v>
+        <v>7189501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,10 +3833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441432</v>
+        <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>91737</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,29 +3844,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759436</v>
+        <v>759321</v>
       </c>
       <c r="R33" t="n">
-        <v>7189501</v>
+        <v>7189301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3917,6 +3912,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>91280</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,45 +2512,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R20" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,32 +2622,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>91280</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R21" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,53 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R22" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441448</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759412</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R30" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,45 +3644,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441448</v>
+        <v>127441405</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759412</v>
+        <v>759321</v>
       </c>
       <c r="R31" t="n">
-        <v>7189523</v>
+        <v>7189301</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3741,27 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441432</v>
+        <v>127441449</v>
       </c>
       <c r="B32" t="n">
-        <v>91737</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759436</v>
+        <v>759381</v>
       </c>
       <c r="R32" t="n">
-        <v>7189501</v>
+        <v>7189520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441405</v>
+        <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>91737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,42 +3862,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759321</v>
+        <v>759436</v>
       </c>
       <c r="R33" t="n">
-        <v>7189301</v>
+        <v>7189501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,11 +3917,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,45 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441445</v>
+        <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759426</v>
+        <v>759415</v>
       </c>
       <c r="R3" t="n">
-        <v>7189499</v>
+        <v>7189526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441443</v>
+        <v>127441445</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759514</v>
+        <v>759426</v>
       </c>
       <c r="R4" t="n">
-        <v>7189412</v>
+        <v>7189499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,53 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441417</v>
+        <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759415</v>
+        <v>759514</v>
       </c>
       <c r="R5" t="n">
-        <v>7189526</v>
+        <v>7189412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,45 +1186,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R7" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R8" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441394</v>
+        <v>127441435</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759332</v>
+        <v>759492</v>
       </c>
       <c r="R9" t="n">
-        <v>7189575</v>
+        <v>7189426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441435</v>
+        <v>127441442</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759492</v>
+        <v>759523</v>
       </c>
       <c r="R10" t="n">
-        <v>7189426</v>
+        <v>7189420</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,10 +1587,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441442</v>
+        <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759345</v>
       </c>
       <c r="R11" t="n">
-        <v>7189420</v>
+        <v>7189493</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,45 +1684,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441450</v>
+        <v>127441394</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759345</v>
+        <v>759332</v>
       </c>
       <c r="R12" t="n">
-        <v>7189493</v>
+        <v>7189575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,6 +1763,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>91280</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R19" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,53 +2512,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R20" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>91280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R21" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,53 +3036,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R25" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,11 +3107,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B26" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3157,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,7 +3166,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3189,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R26" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,7 +3216,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3256,45 +3243,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B27" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R27" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,6 +3322,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441448</v>
+        <v>127441449</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759412</v>
+        <v>759381</v>
       </c>
       <c r="R29" t="n">
-        <v>7189523</v>
+        <v>7189520</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,32 +3547,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441393</v>
+        <v>127441448</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759507</v>
+        <v>759412</v>
       </c>
       <c r="R30" t="n">
-        <v>7189390</v>
+        <v>7189523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441405</v>
+        <v>127441432</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>91737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3655,42 +3655,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759321</v>
+        <v>759436</v>
       </c>
       <c r="R31" t="n">
-        <v>7189301</v>
+        <v>7189501</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3710,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,32 +3736,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R32" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,10 +3833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441432</v>
+        <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>91737</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,29 +3844,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759436</v>
+        <v>759321</v>
       </c>
       <c r="R33" t="n">
-        <v>7189501</v>
+        <v>7189301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3917,6 +3912,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>80025</v>
+        <v>91688</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R13" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>91688</v>
+        <v>80025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R14" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3036,45 +3036,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>57821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R25" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,6 +3115,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,53 +3146,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R26" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,11 +3217,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B27" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R27" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,32 +3450,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>98448</v>
+        <v>91330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441448</v>
+        <v>127441449</v>
       </c>
       <c r="B30" t="n">
         <v>98448</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759412</v>
+        <v>759381</v>
       </c>
       <c r="R30" t="n">
-        <v>7189523</v>
+        <v>7189520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,27 +3644,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441432</v>
+        <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>91737</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3679,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759436</v>
+        <v>759412</v>
       </c>
       <c r="R31" t="n">
-        <v>7189501</v>
+        <v>7189523</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,10 +3741,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441393</v>
+        <v>127441432</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>91737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,21 +3752,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759507</v>
+        <v>759436</v>
       </c>
       <c r="R32" t="n">
-        <v>7189390</v>
+        <v>7189501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,53 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441417</v>
+        <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759415</v>
+        <v>759426</v>
       </c>
       <c r="R3" t="n">
-        <v>7189526</v>
+        <v>7189499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441445</v>
+        <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759426</v>
+        <v>759514</v>
       </c>
       <c r="R4" t="n">
-        <v>7189499</v>
+        <v>7189412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,45 +979,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441443</v>
+        <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759514</v>
+        <v>759415</v>
       </c>
       <c r="R5" t="n">
-        <v>7189412</v>
+        <v>7189526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441435</v>
+        <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759492</v>
+        <v>759332</v>
       </c>
       <c r="R9" t="n">
-        <v>7189426</v>
+        <v>7189575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441442</v>
+        <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759523</v>
+        <v>759492</v>
       </c>
       <c r="R10" t="n">
-        <v>7189420</v>
+        <v>7189426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441450</v>
+        <v>127441442</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759345</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7189493</v>
+        <v>7189420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,53 +1697,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441394</v>
+        <v>127441450</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759332</v>
+        <v>759345</v>
       </c>
       <c r="R12" t="n">
-        <v>7189575</v>
+        <v>7189493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,11 +1768,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1797,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127441423</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>127441402</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>91282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,45 +2512,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R20" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,32 +2622,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441419</v>
+        <v>127441436</v>
       </c>
       <c r="B21" t="n">
-        <v>91280</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759497</v>
+        <v>759452</v>
       </c>
       <c r="R21" t="n">
-        <v>7189429</v>
+        <v>7189432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,53 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R22" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2819,7 +2819,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R25" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3146,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R26" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,6 +3225,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,53 +3256,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R27" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,11 +3327,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,7 +3356,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441405</v>
       </c>
       <c r="B29" t="n">
-        <v>91330</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,34 +3461,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759321</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,6 +3529,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441449</v>
+        <v>127441448</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759381</v>
+        <v>759412</v>
       </c>
       <c r="R30" t="n">
-        <v>7189520</v>
+        <v>7189523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,32 +3657,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441448</v>
+        <v>127441432</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>91739</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3679,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759412</v>
+        <v>759436</v>
       </c>
       <c r="R31" t="n">
-        <v>7189523</v>
+        <v>7189501</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,27 +3749,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441432</v>
+        <v>127441449</v>
       </c>
       <c r="B32" t="n">
-        <v>91737</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759436</v>
+        <v>759381</v>
       </c>
       <c r="R32" t="n">
-        <v>7189501</v>
+        <v>7189520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,42 +3857,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R33" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,11 +3917,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57483</v>
+        <v>57485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,45 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441445</v>
+        <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759426</v>
+        <v>759415</v>
       </c>
       <c r="R3" t="n">
-        <v>7189499</v>
+        <v>7189526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441443</v>
+        <v>127441445</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -917,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759514</v>
+        <v>759426</v>
       </c>
       <c r="R4" t="n">
-        <v>7189412</v>
+        <v>7189499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,53 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441417</v>
+        <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759415</v>
+        <v>759514</v>
       </c>
       <c r="R5" t="n">
-        <v>7189526</v>
+        <v>7189412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R17" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R18" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,7 +2622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441436</v>
+        <v>127441440</v>
       </c>
       <c r="B21" t="n">
         <v>98450</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759452</v>
+        <v>759335</v>
       </c>
       <c r="R21" t="n">
-        <v>7189432</v>
+        <v>7189358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441440</v>
+        <v>127441436</v>
       </c>
       <c r="B22" t="n">
         <v>98450</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759335</v>
+        <v>759452</v>
       </c>
       <c r="R22" t="n">
-        <v>7189358</v>
+        <v>7189432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441398</v>
+        <v>127441418</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759258</v>
+        <v>759318</v>
       </c>
       <c r="R25" t="n">
-        <v>7189373</v>
+        <v>7189338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,53 +3146,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441418</v>
+        <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759318</v>
+        <v>759369</v>
       </c>
       <c r="R26" t="n">
-        <v>7189338</v>
+        <v>7189531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,11 +3217,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3256,45 +3243,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441437</v>
+        <v>127441398</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759369</v>
+        <v>759258</v>
       </c>
       <c r="R27" t="n">
-        <v>7189531</v>
+        <v>7189373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,6 +3322,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>91332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,42 +3461,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,11 +3521,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,45 +3547,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441448</v>
+        <v>127441405</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759412</v>
+        <v>759321</v>
       </c>
       <c r="R30" t="n">
-        <v>7189523</v>
+        <v>7189301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3631,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,27 +3657,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441432</v>
+        <v>127441449</v>
       </c>
       <c r="B31" t="n">
-        <v>91739</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759436</v>
+        <v>759381</v>
       </c>
       <c r="R31" t="n">
-        <v>7189501</v>
+        <v>7189520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3749,7 +3754,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441449</v>
+        <v>127441448</v>
       </c>
       <c r="B32" t="n">
         <v>98450</v>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759381</v>
+        <v>759412</v>
       </c>
       <c r="R32" t="n">
-        <v>7189520</v>
+        <v>7189523</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441393</v>
+        <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>91332</v>
+        <v>91739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3857,21 +3862,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759507</v>
+        <v>759436</v>
       </c>
       <c r="R33" t="n">
-        <v>7189390</v>
+        <v>7189501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,53 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441417</v>
+        <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759415</v>
+        <v>759426</v>
       </c>
       <c r="R3" t="n">
-        <v>7189526</v>
+        <v>7189499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441445</v>
+        <v>127441443</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -930,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759426</v>
+        <v>759514</v>
       </c>
       <c r="R4" t="n">
-        <v>7189499</v>
+        <v>7189412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,45 +979,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441443</v>
+        <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759514</v>
+        <v>759415</v>
       </c>
       <c r="R5" t="n">
-        <v>7189412</v>
+        <v>7189526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,53 +1186,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R7" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,45 +1283,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R8" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1362,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>91282</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R19" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,53 +2512,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R20" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>91282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R21" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R36" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,27 +4242,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B37" t="n">
-        <v>57485</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4280,7 +4275,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4290,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R37" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,45 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441445</v>
+        <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759426</v>
+        <v>759415</v>
       </c>
       <c r="R3" t="n">
-        <v>7189499</v>
+        <v>7189526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441443</v>
+        <v>127441445</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -917,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759514</v>
+        <v>759426</v>
       </c>
       <c r="R4" t="n">
-        <v>7189412</v>
+        <v>7189499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,53 +992,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441417</v>
+        <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759415</v>
+        <v>759514</v>
       </c>
       <c r="R5" t="n">
-        <v>7189526</v>
+        <v>7189412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441394</v>
+        <v>127441442</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759332</v>
+        <v>759523</v>
       </c>
       <c r="R9" t="n">
-        <v>7189575</v>
+        <v>7189420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1587,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441442</v>
+        <v>127441450</v>
       </c>
       <c r="B11" t="n">
         <v>98450</v>
@@ -1635,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759345</v>
       </c>
       <c r="R11" t="n">
-        <v>7189420</v>
+        <v>7189493</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,45 +1684,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441450</v>
+        <v>127441394</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759345</v>
+        <v>759332</v>
       </c>
       <c r="R12" t="n">
-        <v>7189493</v>
+        <v>7189575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,6 +1763,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B13" t="n">
-        <v>91690</v>
+        <v>80027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R13" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B14" t="n">
-        <v>80027</v>
+        <v>91690</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R14" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>91282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441419</v>
+        <v>127441399</v>
       </c>
       <c r="B21" t="n">
-        <v>91282</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,34 +2620,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759497</v>
+        <v>759246</v>
       </c>
       <c r="R21" t="n">
-        <v>7189429</v>
+        <v>7189362</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,6 +2688,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2706,53 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R22" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R25" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3146,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R26" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,6 +3225,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,53 +3256,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R27" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,11 +3327,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441405</v>
       </c>
       <c r="B29" t="n">
-        <v>91332</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,34 +3461,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759321</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,6 +3529,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,53 +3560,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441405</v>
+        <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759321</v>
+        <v>759381</v>
       </c>
       <c r="R30" t="n">
-        <v>7189301</v>
+        <v>7189520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,11 +3631,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,7 +3657,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441449</v>
+        <v>127441448</v>
       </c>
       <c r="B31" t="n">
         <v>98450</v>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759381</v>
+        <v>759412</v>
       </c>
       <c r="R31" t="n">
-        <v>7189520</v>
+        <v>7189523</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,32 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441448</v>
+        <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759412</v>
+        <v>759507</v>
       </c>
       <c r="R32" t="n">
-        <v>7189523</v>
+        <v>7189390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57485</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R36" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,6 +4216,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4242,27 +4247,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4275,7 +4280,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R37" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>127441445</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,45 +1186,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R7" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R8" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441442</v>
+        <v>127441435</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759523</v>
+        <v>759492</v>
       </c>
       <c r="R9" t="n">
-        <v>7189420</v>
+        <v>7189426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,10 +1490,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441435</v>
+        <v>127441442</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759492</v>
+        <v>759523</v>
       </c>
       <c r="R10" t="n">
-        <v>7189426</v>
+        <v>7189420</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>80027</v>
+        <v>91696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R13" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>91690</v>
+        <v>80027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R14" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R17" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R18" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,7 +2418,7 @@
         <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>91282</v>
+        <v>91288</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,45 +2512,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R20" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,53 +2622,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R21" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,11 +2693,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441440</v>
+        <v>127441436</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759335</v>
+        <v>759452</v>
       </c>
       <c r="R22" t="n">
-        <v>7189358</v>
+        <v>7189432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441398</v>
+        <v>127441418</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759258</v>
+        <v>759318</v>
       </c>
       <c r="R25" t="n">
-        <v>7189373</v>
+        <v>7189338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,53 +3146,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441418</v>
+        <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759318</v>
+        <v>759369</v>
       </c>
       <c r="R26" t="n">
-        <v>7189338</v>
+        <v>7189531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,11 +3217,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3256,45 +3243,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441437</v>
+        <v>127441398</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759369</v>
+        <v>759258</v>
       </c>
       <c r="R27" t="n">
-        <v>7189531</v>
+        <v>7189373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,6 +3322,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>91338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,42 +3461,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,11 +3521,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,45 +3547,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441449</v>
+        <v>127441405</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759381</v>
+        <v>759321</v>
       </c>
       <c r="R30" t="n">
-        <v>7189520</v>
+        <v>7189301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3631,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3660,7 +3660,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,32 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441393</v>
+        <v>127441449</v>
       </c>
       <c r="B32" t="n">
-        <v>91332</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759507</v>
+        <v>759381</v>
       </c>
       <c r="R32" t="n">
-        <v>7189390</v>
+        <v>7189520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
         <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127441445</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>127441435</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>127441442</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>127441394</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R17" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B18" t="n">
         <v>57663</v>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R18" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>91288</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R19" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,53 +2512,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R20" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>91291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R21" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2819,7 +2819,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127441418</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>127441398</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441449</v>
       </c>
       <c r="B29" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759381</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189520</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,53 +3547,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441405</v>
+        <v>127441448</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759321</v>
+        <v>759412</v>
       </c>
       <c r="R30" t="n">
-        <v>7189301</v>
+        <v>7189523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,11 +3618,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,45 +3644,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441448</v>
+        <v>127441405</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759412</v>
+        <v>759321</v>
       </c>
       <c r="R31" t="n">
-        <v>7189523</v>
+        <v>7189301</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3728,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,32 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R32" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
         <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57485</v>
+        <v>57488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127441417</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>127441445</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127441443</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,53 +1186,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R7" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,45 +1283,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R8" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1362,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441435</v>
+        <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759492</v>
+        <v>759332</v>
       </c>
       <c r="R9" t="n">
-        <v>7189426</v>
+        <v>7189575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441442</v>
+        <v>127441450</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759523</v>
+        <v>759345</v>
       </c>
       <c r="R10" t="n">
-        <v>7189420</v>
+        <v>7189493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441450</v>
+        <v>127441442</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1622,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759345</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7189493</v>
+        <v>7189420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,53 +1697,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441394</v>
+        <v>127441435</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759332</v>
+        <v>759492</v>
       </c>
       <c r="R12" t="n">
-        <v>7189575</v>
+        <v>7189426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,11 +1768,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,7 +1797,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R17" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R18" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,7 +2418,7 @@
         <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,32 +2512,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441436</v>
+        <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>91299</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759452</v>
+        <v>759497</v>
       </c>
       <c r="R20" t="n">
-        <v>7189432</v>
+        <v>7189429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441419</v>
+        <v>127441436</v>
       </c>
       <c r="B21" t="n">
-        <v>91291</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759497</v>
+        <v>759452</v>
       </c>
       <c r="R21" t="n">
-        <v>7189429</v>
+        <v>7189432</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R25" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,7 +3149,7 @@
         <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441398</v>
+        <v>127441418</v>
       </c>
       <c r="B27" t="n">
-        <v>57666</v>
+        <v>57832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759258</v>
+        <v>759318</v>
       </c>
       <c r="R27" t="n">
-        <v>7189373</v>
+        <v>7189338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3356,7 +3356,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,45 +3450,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441449</v>
+        <v>127441405</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759381</v>
+        <v>759321</v>
       </c>
       <c r="R29" t="n">
-        <v>7189520</v>
+        <v>7189301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,6 +3529,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441448</v>
+        <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759412</v>
+        <v>759381</v>
       </c>
       <c r="R30" t="n">
-        <v>7189523</v>
+        <v>7189520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441405</v>
+        <v>127441432</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>91756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3655,42 +3668,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759321</v>
+        <v>759436</v>
       </c>
       <c r="R31" t="n">
-        <v>7189301</v>
+        <v>7189501</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3723,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,7 +3752,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,27 +3846,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441432</v>
+        <v>127441448</v>
       </c>
       <c r="B33" t="n">
-        <v>91748</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759436</v>
+        <v>759412</v>
       </c>
       <c r="R33" t="n">
-        <v>7189501</v>
+        <v>7189523</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57488</v>
+        <v>57494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -785,53 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127441417</v>
+        <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759415</v>
+        <v>759426</v>
       </c>
       <c r="R3" t="n">
-        <v>7189526</v>
+        <v>7189499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +856,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441445</v>
+        <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759426</v>
+        <v>759514</v>
       </c>
       <c r="R4" t="n">
-        <v>7189499</v>
+        <v>7189412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,45 +979,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441443</v>
+        <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759514</v>
+        <v>759415</v>
       </c>
       <c r="R5" t="n">
-        <v>7189412</v>
+        <v>7189526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1058,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,45 +1186,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R7" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R8" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441394</v>
+        <v>127441442</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759332</v>
+        <v>759523</v>
       </c>
       <c r="R9" t="n">
-        <v>7189575</v>
+        <v>7189420</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1493,7 @@
         <v>127441450</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,45 +1587,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441442</v>
+        <v>127441394</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759332</v>
       </c>
       <c r="R11" t="n">
-        <v>7189420</v>
+        <v>7189575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,6 +1666,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1700,7 @@
         <v>127441435</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,45 +2415,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441399</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759246</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,6 +2494,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,32 +2525,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441419</v>
+        <v>127441436</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759497</v>
+        <v>759452</v>
       </c>
       <c r="R20" t="n">
-        <v>7189429</v>
+        <v>7189432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,32 +2622,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441436</v>
+        <v>127441419</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>91300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759452</v>
+        <v>759497</v>
       </c>
       <c r="R21" t="n">
-        <v>7189432</v>
+        <v>7189429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,53 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R22" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,53 +3036,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R25" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,11 +3107,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3133,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R26" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,6 +3212,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B27" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R27" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,42 +3461,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,11 +3521,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,45 +3547,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441449</v>
+        <v>127441405</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759381</v>
+        <v>759321</v>
       </c>
       <c r="R30" t="n">
-        <v>7189520</v>
+        <v>7189301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3631,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,27 +3657,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441432</v>
+        <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>91756</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759436</v>
+        <v>759412</v>
       </c>
       <c r="R31" t="n">
-        <v>7189501</v>
+        <v>7189523</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3749,32 +3754,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441393</v>
+        <v>127441449</v>
       </c>
       <c r="B32" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759507</v>
+        <v>759381</v>
       </c>
       <c r="R32" t="n">
-        <v>7189390</v>
+        <v>7189520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,32 +3851,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441448</v>
+        <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>91757</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759412</v>
+        <v>759436</v>
       </c>
       <c r="R33" t="n">
-        <v>7189523</v>
+        <v>7189501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R36" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,27 +4242,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4280,7 +4275,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4290,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R37" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441442</v>
+        <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759523</v>
+        <v>759332</v>
       </c>
       <c r="R9" t="n">
-        <v>7189420</v>
+        <v>7189575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,7 +1503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441450</v>
+        <v>127441435</v>
       </c>
       <c r="B10" t="n">
         <v>98468</v>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759345</v>
+        <v>759492</v>
       </c>
       <c r="R10" t="n">
-        <v>7189493</v>
+        <v>7189426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,53 +1600,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441394</v>
+        <v>127441442</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759332</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7189575</v>
+        <v>7189420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,11 +1671,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,7 +1697,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441435</v>
+        <v>127441450</v>
       </c>
       <c r="B12" t="n">
         <v>98468</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759492</v>
+        <v>759345</v>
       </c>
       <c r="R12" t="n">
-        <v>7189426</v>
+        <v>7189493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2415,53 +2415,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441399</v>
+        <v>127441440</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759246</v>
+        <v>759335</v>
       </c>
       <c r="R19" t="n">
-        <v>7189362</v>
+        <v>7189358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,11 +2486,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441440</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759335</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189358</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,45 +3036,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R25" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,6 +3115,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,53 +3146,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441418</v>
+        <v>127441437</v>
       </c>
       <c r="B26" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759318</v>
+        <v>759369</v>
       </c>
       <c r="R26" t="n">
-        <v>7189338</v>
+        <v>7189531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,11 +3217,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441405</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,34 +3461,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759321</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189301</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,6 +3529,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,42 +3571,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R30" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,11 +3631,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,7 +3657,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441448</v>
+        <v>127441449</v>
       </c>
       <c r="B31" t="n">
         <v>98468</v>
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759412</v>
+        <v>759381</v>
       </c>
       <c r="R31" t="n">
-        <v>7189523</v>
+        <v>7189520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441449</v>
+        <v>127441448</v>
       </c>
       <c r="B32" t="n">
         <v>98468</v>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759381</v>
+        <v>759412</v>
       </c>
       <c r="R32" t="n">
-        <v>7189520</v>
+        <v>7189523</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R36" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,6 +4216,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4242,27 +4247,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4275,7 +4280,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R37" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>127441442</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>127441450</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B13" t="n">
-        <v>91708</v>
+        <v>80036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R13" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B14" t="n">
-        <v>80036</v>
+        <v>91709</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R14" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441440</v>
+        <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>91301</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759335</v>
+        <v>759497</v>
       </c>
       <c r="R19" t="n">
-        <v>7189358</v>
+        <v>7189429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,45 +2512,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R20" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,6 +2591,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,32 +2622,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127441419</v>
+        <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>91300</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759497</v>
+        <v>759335</v>
       </c>
       <c r="R21" t="n">
-        <v>7189429</v>
+        <v>7189358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2706,53 +2719,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441399</v>
+        <v>127441436</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759246</v>
+        <v>759452</v>
       </c>
       <c r="R22" t="n">
-        <v>7189362</v>
+        <v>7189432</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,11 +2790,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127441418</v>
+        <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3069,7 +3069,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759318</v>
+        <v>759258</v>
       </c>
       <c r="R25" t="n">
-        <v>7189338</v>
+        <v>7189373</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,45 +3146,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127441437</v>
+        <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759369</v>
+        <v>759318</v>
       </c>
       <c r="R26" t="n">
-        <v>7189531</v>
+        <v>7189338</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,6 +3225,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3243,53 +3256,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127441398</v>
+        <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759258</v>
+        <v>759369</v>
       </c>
       <c r="R27" t="n">
-        <v>7189373</v>
+        <v>7189531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,11 +3327,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,42 +3461,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R29" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,11 +3521,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441393</v>
+        <v>127441405</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,34 +3558,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759507</v>
+        <v>759321</v>
       </c>
       <c r="R30" t="n">
-        <v>7189390</v>
+        <v>7189301</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3631,6 +3626,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3660,7 +3660,7 @@
         <v>127441449</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>127441448</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R36" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,27 +4242,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4280,7 +4275,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4290,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R37" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441394</v>
+        <v>127441450</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759332</v>
+        <v>759345</v>
       </c>
       <c r="R9" t="n">
-        <v>7189575</v>
+        <v>7189493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1464,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,45 +1490,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441435</v>
+        <v>127441394</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759492</v>
+        <v>759332</v>
       </c>
       <c r="R10" t="n">
-        <v>7189426</v>
+        <v>7189575</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,6 +1569,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1600,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441442</v>
+        <v>127441435</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759492</v>
       </c>
       <c r="R11" t="n">
-        <v>7189420</v>
+        <v>7189426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441450</v>
+        <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759345</v>
+        <v>759523</v>
       </c>
       <c r="R12" t="n">
-        <v>7189493</v>
+        <v>7189420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127441425</v>
+        <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>80036</v>
+        <v>91710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759333</v>
+        <v>759508</v>
       </c>
       <c r="R13" t="n">
-        <v>7189515</v>
+        <v>7189383</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127441392</v>
+        <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>91709</v>
+        <v>80036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759508</v>
+        <v>759333</v>
       </c>
       <c r="R14" t="n">
-        <v>7189383</v>
+        <v>7189515</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R17" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R18" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,7 +2418,7 @@
         <v>127441419</v>
       </c>
       <c r="B19" t="n">
-        <v>91301</v>
+        <v>91302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>127441436</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,32 +3450,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441393</v>
+        <v>127441448</v>
       </c>
       <c r="B29" t="n">
-        <v>91351</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759507</v>
+        <v>759412</v>
       </c>
       <c r="R29" t="n">
-        <v>7189390</v>
+        <v>7189523</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441405</v>
+        <v>127441393</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,42 +3558,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759321</v>
+        <v>759507</v>
       </c>
       <c r="R30" t="n">
-        <v>7189301</v>
+        <v>7189390</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,11 +3618,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,45 +3644,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441449</v>
+        <v>127441405</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759381</v>
+        <v>759321</v>
       </c>
       <c r="R31" t="n">
-        <v>7189520</v>
+        <v>7189301</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3728,6 +3723,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441448</v>
+        <v>127441449</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759412</v>
+        <v>759381</v>
       </c>
       <c r="R32" t="n">
-        <v>7189523</v>
+        <v>7189520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
         <v>127441432</v>
       </c>
       <c r="B33" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R36" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,6 +4216,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4242,27 +4247,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4275,7 +4280,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R37" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -1186,53 +1186,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R7" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,11 +1257,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,45 +1283,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R8" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,6 +1362,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441450</v>
+        <v>127441435</v>
       </c>
       <c r="B9" t="n">
         <v>98470</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759345</v>
+        <v>759492</v>
       </c>
       <c r="R9" t="n">
-        <v>7189493</v>
+        <v>7189426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,53 +1490,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441394</v>
+        <v>127441450</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759332</v>
+        <v>759345</v>
       </c>
       <c r="R10" t="n">
-        <v>7189575</v>
+        <v>7189493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,11 +1561,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1600,7 +1587,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441435</v>
+        <v>127441442</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1635,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759492</v>
+        <v>759523</v>
       </c>
       <c r="R11" t="n">
-        <v>7189426</v>
+        <v>7189420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,45 +1684,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441442</v>
+        <v>127441394</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759523</v>
+        <v>759332</v>
       </c>
       <c r="R12" t="n">
-        <v>7189420</v>
+        <v>7189575</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,6 +1763,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R17" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R18" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2415,32 +2415,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127441419</v>
+        <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>91302</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759497</v>
+        <v>759452</v>
       </c>
       <c r="R19" t="n">
-        <v>7189429</v>
+        <v>7189432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127441399</v>
+        <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>91302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,42 +2523,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759246</v>
+        <v>759497</v>
       </c>
       <c r="R20" t="n">
-        <v>7189362</v>
+        <v>7189429</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,45 +2706,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127441436</v>
+        <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759452</v>
+        <v>759246</v>
       </c>
       <c r="R22" t="n">
-        <v>7189432</v>
+        <v>7189362</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,6 +2785,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3450,32 +3450,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127441448</v>
+        <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>91759</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759412</v>
+        <v>759436</v>
       </c>
       <c r="R29" t="n">
-        <v>7189523</v>
+        <v>7189501</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,32 +3542,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127441393</v>
+        <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3577,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759507</v>
+        <v>759381</v>
       </c>
       <c r="R30" t="n">
-        <v>7189390</v>
+        <v>7189520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3644,53 +3639,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127441405</v>
+        <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759321</v>
+        <v>759412</v>
       </c>
       <c r="R31" t="n">
-        <v>7189301</v>
+        <v>7189523</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3723,11 +3710,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,32 +3736,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127441449</v>
+        <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3789,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>759381</v>
+        <v>759507</v>
       </c>
       <c r="R32" t="n">
-        <v>7189520</v>
+        <v>7189390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,10 +3833,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127441432</v>
+        <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>91759</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,29 +3844,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>759436</v>
+        <v>759321</v>
       </c>
       <c r="R33" t="n">
-        <v>7189501</v>
+        <v>7189301</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3917,6 +3912,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R36" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,11 +4216,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,27 +4242,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4280,7 +4275,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4290,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R37" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4326,6 +4321,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -1186,45 +1186,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127441444</v>
+        <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759448</v>
+        <v>759297</v>
       </c>
       <c r="R7" t="n">
-        <v>7189482</v>
+        <v>7189326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,6 +1265,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127441403</v>
+        <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759297</v>
+        <v>759448</v>
       </c>
       <c r="R8" t="n">
-        <v>7189326</v>
+        <v>7189482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1367,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127441435</v>
+        <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759492</v>
+        <v>759332</v>
       </c>
       <c r="R9" t="n">
-        <v>7189426</v>
+        <v>7189575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,6 +1472,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,7 +1503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127441450</v>
+        <v>127441435</v>
       </c>
       <c r="B10" t="n">
         <v>98470</v>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759345</v>
+        <v>759492</v>
       </c>
       <c r="R10" t="n">
-        <v>7189493</v>
+        <v>7189426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1600,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127441442</v>
+        <v>127441450</v>
       </c>
       <c r="B11" t="n">
         <v>98470</v>
@@ -1622,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759523</v>
+        <v>759345</v>
       </c>
       <c r="R11" t="n">
-        <v>7189420</v>
+        <v>7189493</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,53 +1697,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127441394</v>
+        <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blekberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759332</v>
+        <v>759523</v>
       </c>
       <c r="R12" t="n">
-        <v>7189575</v>
+        <v>7189420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,11 +1768,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127441423</v>
+        <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759438</v>
+        <v>759287</v>
       </c>
       <c r="R17" t="n">
-        <v>7189512</v>
+        <v>7189335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127441402</v>
+        <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759287</v>
+        <v>759438</v>
       </c>
       <c r="R18" t="n">
-        <v>7189335</v>
+        <v>7189512</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4137,27 +4137,27 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127441413</v>
+        <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102976</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>759540</v>
+        <v>759256</v>
       </c>
       <c r="R36" t="n">
-        <v>7189357</v>
+        <v>7189341</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,6 +4216,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4242,27 +4247,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127441401</v>
+        <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>102976</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4275,7 +4280,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>759256</v>
+        <v>759540</v>
       </c>
       <c r="R37" t="n">
-        <v>7189341</v>
+        <v>7189357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4321,11 +4326,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,14 +781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,14 +882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,14 +983,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,14 +1097,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,14 +1198,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,14 +1312,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,14 +1413,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,14 +1527,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,14 +1628,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,14 +1729,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,14 +1830,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91710</v>
+        <v>91862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,14 +1931,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80036</v>
+        <v>80129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,14 +2032,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,14 +2133,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,14 +2247,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,14 +2361,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,14 +2475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,14 +2576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91302</v>
+        <v>91454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,14 +2677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,14 +2778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,14 +2892,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,14 +3006,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,14 +3120,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3142,14 +3234,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,14 +3348,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,14 +3449,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,14 +3550,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91759</v>
+        <v>91911</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,14 +3646,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,14 +3747,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3732,14 +3848,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,14 +3949,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3939,14 +4063,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,14 +4164,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,14 +4265,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,14 +4379,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57537</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4348,14 +4488,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4602,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91911</v>
+        <v>91915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57537</v>
+        <v>57541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57541</v>
+        <v>57544</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91928</v>
+        <v>91931</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91934</v>
+        <v>91941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57544</v>
+        <v>57546</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91941</v>
+        <v>91948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127441421</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127441417</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127441403</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>127441394</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>127441406</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>127441402</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>127441423</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127441399</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>127441395</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>127441422</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>127441398</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>127441418</v>
       </c>
       <c r="B26" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91948</v>
+        <v>91950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>127441405</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>127441401</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>127441413</v>
       </c>
       <c r="B37" t="n">
-        <v>57546</v>
+        <v>57548</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>127441400</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91950</v>
+        <v>91958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91959</v>
+        <v>91962</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>127441425</v>
       </c>
       <c r="B14" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>127441455</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91962</v>
+        <v>91964</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 36480-2025 artfynd.xlsx
+++ b/artfynd/A 36480-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>127441445</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127441443</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>127441439</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>127441444</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>127441435</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>127441450</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>127441442</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>127441392</v>
       </c>
       <c r="B13" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>127441438</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>127441436</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>127441419</v>
       </c>
       <c r="B20" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127441440</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>127441437</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127441432</v>
       </c>
       <c r="B29" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>127441449</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>127441448</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>127441393</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>127441441</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>127441447</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
